--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C11894F-27BC-2748-B7E4-9348EE0E24DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4823B01C-EEFF-E546-B1EA-B8BCE1C68816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17460" yWindow="780" windowWidth="18540" windowHeight="20680" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="17460" yWindow="780" windowWidth="18540" windowHeight="20680" activeTab="1" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -2822,6 +2822,9 @@
                 <c:pt idx="841">
                   <c:v>46269</c:v>
                 </c:pt>
+                <c:pt idx="842">
+                  <c:v>46276</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4855,6 +4858,9 @@
                 </c:pt>
                 <c:pt idx="841">
                   <c:v>2442.9699999999998</c:v>
+                </c:pt>
+                <c:pt idx="842">
+                  <c:v>2447.44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4936,7 +4942,7 @@
         <c:axId val="48971520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="2400"/>
+          <c:max val="2500"/>
           <c:min val="2100"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -4989,6 +4995,7 @@
         <c:crossAx val="48987840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:majorUnit val="100"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -5966,7 +5973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P843"/>
+  <dimension ref="A1:P844"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
@@ -22713,7 +22720,7 @@
         <v>0.66666666666661301</v>
       </c>
       <c r="D843" s="8" t="str">
-        <f t="shared" ref="D843" si="16">"UTC+"&amp;IF(
+        <f t="shared" ref="D843:D844" si="16">"UTC+"&amp;IF(
     AND(
         B843&gt;=EOMONTH(DATE(YEAR(B843),3,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B843),3,1),0),2),7),
         B843&lt;EOMONTH(DATE(YEAR(B843),10,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B843),10,1),0),2),7)
@@ -22754,6 +22761,54 @@
         <v>72000</v>
       </c>
       <c r="O843" s="14">
+        <v>79000</v>
+      </c>
+    </row>
+    <row r="844" spans="1:15">
+      <c r="A844" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B844" s="8">
+        <v>46276</v>
+      </c>
+      <c r="C844" s="9">
+        <v>0.66666666666678398</v>
+      </c>
+      <c r="D844" s="8" t="str">
+        <f t="shared" si="16"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="E844" s="10">
+        <v>2447.44</v>
+      </c>
+      <c r="F844" s="14">
+        <v>11000</v>
+      </c>
+      <c r="G844" s="14">
+        <v>18000</v>
+      </c>
+      <c r="H844" s="14">
+        <v>34500</v>
+      </c>
+      <c r="I844" s="14">
+        <v>37500</v>
+      </c>
+      <c r="J844" s="14">
+        <v>43000</v>
+      </c>
+      <c r="K844" s="14">
+        <v>45000</v>
+      </c>
+      <c r="L844" s="14">
+        <v>49000</v>
+      </c>
+      <c r="M844" s="14">
+        <v>58000</v>
+      </c>
+      <c r="N844" s="14">
+        <v>72000</v>
+      </c>
+      <c r="O844" s="14">
         <v>79000</v>
       </c>
     </row>

--- a/data_lake/freight/HARPEX.xlsx
+++ b/data_lake/freight/HARPEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4823B01C-EEFF-E546-B1EA-B8BCE1C68816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00C4EB2-6DCE-4A47-8C6E-8C78DF0E5405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17460" yWindow="780" windowWidth="18540" windowHeight="20680" activeTab="1" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="29840" yWindow="2500" windowWidth="18540" windowHeight="20680" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -2825,6 +2825,9 @@
                 <c:pt idx="842">
                   <c:v>46276</c:v>
                 </c:pt>
+                <c:pt idx="843">
+                  <c:v>46283</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4861,6 +4864,9 @@
                 </c:pt>
                 <c:pt idx="842">
                   <c:v>2447.44</c:v>
+                </c:pt>
+                <c:pt idx="843">
+                  <c:v>2450.42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5973,7 +5979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P844"/>
+  <dimension ref="A1:P845"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
@@ -22720,7 +22726,7 @@
         <v>0.66666666666661301</v>
       </c>
       <c r="D843" s="8" t="str">
-        <f t="shared" ref="D843:D844" si="16">"UTC+"&amp;IF(
+        <f t="shared" ref="D843:D845" si="16">"UTC+"&amp;IF(
     AND(
         B843&gt;=EOMONTH(DATE(YEAR(B843),3,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B843),3,1),0),2),7),
         B843&lt;EOMONTH(DATE(YEAR(B843),10,1),0)-MOD(WEEKDAY(EOMONTH(DATE(YEAR(B843),10,1),0),2),7)
@@ -22809,6 +22815,54 @@
         <v>72000</v>
       </c>
       <c r="O844" s="14">
+        <v>79000</v>
+      </c>
+    </row>
+    <row r="845" spans="1:15">
+      <c r="A845" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B845" s="8">
+        <v>46283</v>
+      </c>
+      <c r="C845" s="9">
+        <v>0.66666666666644303</v>
+      </c>
+      <c r="D845" s="8" t="str">
+        <f t="shared" si="16"/>
+        <v>UTC+2</v>
+      </c>
+      <c r="E845" s="10">
+        <v>2450.42</v>
+      </c>
+      <c r="F845" s="14">
+        <v>11000</v>
+      </c>
+      <c r="G845" s="14">
+        <v>18000</v>
+      </c>
+      <c r="H845" s="14">
+        <v>35000</v>
+      </c>
+      <c r="I845" s="14">
+        <v>38000</v>
+      </c>
+      <c r="J845" s="14">
+        <v>43000</v>
+      </c>
+      <c r="K845" s="14">
+        <v>45000</v>
+      </c>
+      <c r="L845" s="14">
+        <v>49000</v>
+      </c>
+      <c r="M845" s="14">
+        <v>58000</v>
+      </c>
+      <c r="N845" s="14">
+        <v>72000</v>
+      </c>
+      <c r="O845" s="14">
         <v>79000</v>
       </c>
     </row>
